--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104621_W19.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104621_W19.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.483000000000001</v>
+        <v>7.5113</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1438</v>
+        <v>5.352</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3392</v>
+        <v>2.1593</v>
       </c>
       <c r="G2" t="n">
-        <v>2.601</v>
+        <v>2.5903</v>
       </c>
       <c r="H2" t="n">
-        <v>2.5876</v>
+        <v>2.566</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0134</v>
+        <v>0.0243</v>
       </c>
       <c r="J2" t="n">
-        <v>3.904</v>
+        <v>3.8753</v>
       </c>
       <c r="K2" t="n">
-        <v>2.6353</v>
+        <v>2.6093</v>
       </c>
       <c r="L2" t="n">
-        <v>1.2688</v>
+        <v>1.2661</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.303</v>
+        <v>-1.2851</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0477</v>
+        <v>-0.0433</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.2554</v>
+        <v>-1.2417</v>
       </c>
       <c r="P2" t="n">
-        <v>3.6293</v>
+        <v>3.6421</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>3.6293</v>
+        <v>3.6421</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3208</v>
+        <v>0.3472</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8257</v>
+        <v>0.0717</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4951</v>
+        <v>0.2755</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W2" t="n">
-        <v>1.4141</v>
+        <v>1.405</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.4822</v>
+        <v>-0.4733</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.8384</v>
+        <v>4.4632</v>
       </c>
       <c r="E3" t="n">
-        <v>5.6485</v>
+        <v>6.0168</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.8102</v>
+        <v>-1.5536</v>
       </c>
       <c r="G3" t="n">
-        <v>2.5947</v>
+        <v>2.5799</v>
       </c>
       <c r="H3" t="n">
-        <v>2.4374</v>
+        <v>2.422</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="J3" t="n">
-        <v>5.4271</v>
+        <v>5.3846</v>
       </c>
       <c r="K3" t="n">
-        <v>2.895</v>
+        <v>2.8678</v>
       </c>
       <c r="L3" t="n">
-        <v>2.5321</v>
+        <v>2.5168</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.8325</v>
+        <v>-2.8047</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4576</v>
+        <v>-0.4458</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.3749</v>
+        <v>-2.3588</v>
       </c>
       <c r="P3" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.985</v>
+        <v>-0.3428</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6049</v>
+        <v>-0.1794</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3802</v>
+        <v>-0.1634</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8678</v>
+        <v>0.8603</v>
       </c>
       <c r="W3" t="n">
-        <v>1.9604</v>
+        <v>1.9497</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="4">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8938</v>
+        <v>2.9338</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6667</v>
+        <v>0.586</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2271</v>
+        <v>2.3478</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6375999999999999</v>
+        <v>0.6307</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6072</v>
+        <v>-0.6224</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2449</v>
+        <v>1.2531</v>
       </c>
       <c r="J4" t="n">
-        <v>1.5248</v>
+        <v>1.5013</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.2291</v>
+        <v>-0.2488</v>
       </c>
       <c r="L4" t="n">
-        <v>1.7539</v>
+        <v>1.7501</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8871</v>
+        <v>-0.8706</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3781</v>
+        <v>-0.3736</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.509</v>
+        <v>-0.497</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R4" t="n">
-        <v>3.1757</v>
+        <v>3.1868</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2562</v>
+        <v>0.3031</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3176</v>
+        <v>0.2715</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0614</v>
+        <v>0.0316</v>
       </c>
       <c r="V4" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.939</v>
+        <v>2.4923</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4573</v>
+        <v>2.0727</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4818</v>
+        <v>0.4195</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0248</v>
+        <v>0.0069</v>
       </c>
       <c r="H5" t="n">
-        <v>1.68</v>
+        <v>1.6557</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.6552</v>
+        <v>-1.6487</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3996</v>
+        <v>1.3658</v>
       </c>
       <c r="K5" t="n">
-        <v>2.074</v>
+        <v>2.0437</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6744</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3749</v>
+        <v>-1.3588</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.394</v>
+        <v>-0.3881</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9808</v>
+        <v>-0.9708</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4467</v>
+        <v>0.1195</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6079</v>
+        <v>0.0531</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1612</v>
+        <v>0.0664</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W5" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="6">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.269</v>
+        <v>-0.0885</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3459</v>
+        <v>0.7549</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6149</v>
+        <v>-0.8434</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.6021</v>
+        <v>-1.6006</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5973000000000001</v>
+        <v>-0.6028</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.0048</v>
+        <v>-0.9977</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2336</v>
+        <v>0.2189</v>
       </c>
       <c r="K6" t="n">
-        <v>0.159</v>
+        <v>0.1444</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.8357</v>
+        <v>-1.8194</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7563</v>
+        <v>-0.7472</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.0795</v>
+        <v>-1.0722</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S6" t="n">
-        <v>0.199</v>
+        <v>0.3739</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0484</v>
+        <v>0.3782</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2474</v>
+        <v>-0.0044</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. MEINDL</t>
+          <t>J. RUBIO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.659</v>
+        <v>-1.1734</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2697</v>
+        <v>-0.3434</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.9287</v>
+        <v>-0.8299</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.0511</v>
+        <v>-1.4764</v>
       </c>
       <c r="H7" t="n">
-        <v>1.7606</v>
+        <v>-0.2874</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.8117</v>
+        <v>-1.189</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1364</v>
+        <v>-0.3015</v>
       </c>
       <c r="K7" t="n">
-        <v>2.2023</v>
+        <v>0.0862</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.066</v>
+        <v>-0.3877</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.1875</v>
+        <v>-1.1749</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4417</v>
+        <v>-0.3736</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.7458</v>
+        <v>-0.8012</v>
       </c>
       <c r="P7" t="n">
-        <v>1.361</v>
+        <v>1.5934</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>3.6293</v>
+        <v>1.5934</v>
       </c>
       <c r="S7" t="n">
-        <v>1.6701</v>
+        <v>-0.2009</v>
       </c>
       <c r="T7" t="n">
-        <v>1.0556</v>
+        <v>-0.0419</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6145</v>
+        <v>-0.159</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.639</v>
+        <v>-1.0895</v>
       </c>
       <c r="W7" t="n">
-        <v>2.3461</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.9851</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. ALMAZAN</t>
+          <t>J. AXEL GUDMUNDSSON</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1166</v>
+        <v>-1.2968</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3915</v>
+        <v>-0.9049</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.508</v>
+        <v>-0.3919</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.9626</v>
+        <v>-1.3668</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.7662</v>
+        <v>0.0289</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.1964</v>
+        <v>-1.3957</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.9428</v>
+        <v>-0.6802</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.0417</v>
+        <v>0.0722</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.901</v>
+        <v>-0.7524</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.0198</v>
+        <v>-0.6866</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7245</v>
+        <v>-0.0433</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.2954</v>
+        <v>-0.6433</v>
       </c>
       <c r="P8" t="n">
-        <v>1.8147</v>
+        <v>0.9105</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8147</v>
+        <v>0.9105</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9633</v>
+        <v>0.1775</v>
       </c>
       <c r="T8" t="n">
-        <v>1.1735</v>
+        <v>0.1623</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2102</v>
+        <v>0.0152</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-1.018</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1607</v>
+        <v>-0.387</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0927</v>
+        <v>-0.6311</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. AXEL GUDMUNDSSON</t>
+          <t>P. ALMAZAN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.536</v>
+        <v>-1.5402</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9644</v>
+        <v>-0.2124</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5716</v>
+        <v>-1.3279</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.3649</v>
+        <v>-2.9625</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0318</v>
+        <v>-0.7668</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.3967</v>
+        <v>-2.1957</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6696</v>
+        <v>-0.9575</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0795</v>
+        <v>-0.0485</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.749</v>
+        <v>-0.909</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6954</v>
+        <v>-2.005</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0477</v>
+        <v>-0.7184</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-1.2866</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9073</v>
+        <v>1.8211</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9073</v>
+        <v>1.8211</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0499</v>
+        <v>0.5329</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0907</v>
+        <v>0.5874</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1406</v>
+        <v>-0.0545</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.0285</v>
+        <v>-0.9317</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.3856</v>
+        <v>0.1578</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6429</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. RUBIO</t>
+          <t>L. MEINDL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.5797</v>
+        <v>-1.6754</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6398</v>
+        <v>0.5745</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9399</v>
+        <v>-2.2499</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.4751</v>
+        <v>-2.0665</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2915</v>
+        <v>1.747</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.1835</v>
+        <v>-3.8135</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.292</v>
+        <v>0.092</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0866</v>
+        <v>2.1784</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.3786</v>
+        <v>-2.0864</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1831</v>
+        <v>-2.1585</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3781</v>
+        <v>-0.4314</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.805</v>
+        <v>-1.7271</v>
       </c>
       <c r="P10" t="n">
-        <v>1.5878</v>
+        <v>1.3658</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5878</v>
+        <v>3.6421</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5997</v>
+        <v>0.6595</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3478</v>
+        <v>0.4221</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2519</v>
+        <v>0.2374</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0927</v>
+        <v>-1.6342</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.3367</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0927</v>
+        <v>-3.9709</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.3438</v>
+        <v>-4.2744</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.8653</v>
+        <v>-3.0445</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4785</v>
+        <v>-1.2299</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.6074</v>
+        <v>-2.6131</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1658</v>
+        <v>-0.1747</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.4416</v>
+        <v>-2.4384</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.2325</v>
+        <v>-1.2542</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2282</v>
+        <v>0.2133</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.4608</v>
+        <v>-1.4676</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.3749</v>
+        <v>-1.3588</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.394</v>
+        <v>-0.3881</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9808</v>
+        <v>-0.9708</v>
       </c>
       <c r="P11" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.5264</v>
+        <v>-0.4612</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.113</v>
+        <v>-0.2652</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4134</v>
+        <v>-0.1961</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.571</v>
+        <v>-2.5659</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.650100000000002</v>
+        <v>7.351899999999997</v>
       </c>
       <c r="E12" t="n">
-        <v>10.4539</v>
+        <v>10.8517</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.803700000000001</v>
+        <v>-3.499900000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>-6.205100000000001</v>
+        <v>-6.2781</v>
       </c>
       <c r="H12" t="n">
-        <v>6.0694</v>
+        <v>5.9655</v>
       </c>
       <c r="I12" t="n">
-        <v>-12.2743</v>
+        <v>-12.2434</v>
       </c>
       <c r="J12" t="n">
-        <v>9.4886</v>
+        <v>9.244499999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>10.0891</v>
+        <v>9.917999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6004000000000003</v>
+        <v>-0.6734999999999993</v>
       </c>
       <c r="M12" t="n">
-        <v>-15.6939</v>
+        <v>-15.5224</v>
       </c>
       <c r="N12" t="n">
-        <v>-4.0197</v>
+        <v>-3.9528</v>
       </c>
       <c r="O12" t="n">
-        <v>-11.6743</v>
+        <v>-11.5695</v>
       </c>
       <c r="P12" t="n">
-        <v>15.8783</v>
+        <v>15.9343</v>
       </c>
       <c r="Q12" t="n">
-        <v>-7.9392</v>
+        <v>-7.967200000000001</v>
       </c>
       <c r="R12" t="n">
-        <v>23.8175</v>
+        <v>23.9012</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8016999999999996</v>
+        <v>1.5087</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7410999999999999</v>
+        <v>1.4598</v>
       </c>
       <c r="U12" t="n">
-        <v>0.06050000000000011</v>
+        <v>0.04870000000000005</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.8244</v>
+        <v>-3.8131</v>
       </c>
       <c r="W12" t="n">
-        <v>8.1632</v>
+        <v>8.1145</v>
       </c>
       <c r="X12" t="n">
-        <v>-11.9877</v>
+        <v>-11.9277</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.5332</v>
+        <v>6.1176</v>
       </c>
       <c r="E13" t="n">
-        <v>7.7748</v>
+        <v>7.713</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.2415</v>
+        <v>-1.5953</v>
       </c>
       <c r="G13" t="n">
-        <v>6.7455</v>
+        <v>6.7516</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.0479</v>
+        <v>-2.026</v>
       </c>
       <c r="I13" t="n">
-        <v>8.7934</v>
+        <v>8.7776</v>
       </c>
       <c r="J13" t="n">
-        <v>8.374700000000001</v>
+        <v>8.3415</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.6132</v>
+        <v>-0.6173</v>
       </c>
       <c r="L13" t="n">
-        <v>8.9879</v>
+        <v>8.9587</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.6292</v>
+        <v>-1.5899</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.4347</v>
+        <v>-1.4087</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1945</v>
+        <v>-0.1811</v>
       </c>
       <c r="P13" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="Q13" t="n">
-        <v>-4.7635</v>
+        <v>-4.7803</v>
       </c>
       <c r="R13" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4579</v>
+        <v>0.1372</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1785</v>
+        <v>0.1808</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6364</v>
+        <v>-0.0436</v>
       </c>
       <c r="V13" t="n">
-        <v>2.6481</v>
+        <v>2.6433</v>
       </c>
       <c r="W13" t="n">
-        <v>3.9851</v>
+        <v>3.9709</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.337</v>
+        <v>-1.3276</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.0263</v>
+        <v>2.9916</v>
       </c>
       <c r="E14" t="n">
-        <v>2.8118</v>
+        <v>3.0375</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2145</v>
+        <v>-0.0459</v>
       </c>
       <c r="G14" t="n">
-        <v>1.092</v>
+        <v>1.1008</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0605</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>1.0316</v>
+        <v>1.0323</v>
       </c>
       <c r="J14" t="n">
-        <v>2.1546</v>
+        <v>2.1479</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8485</v>
+        <v>0.8446</v>
       </c>
       <c r="L14" t="n">
-        <v>1.3061</v>
+        <v>1.3033</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.0626</v>
+        <v>-1.0471</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.788</v>
+        <v>-0.7761</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2745</v>
+        <v>-0.271</v>
       </c>
       <c r="P14" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2447</v>
+        <v>0.1988</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2087</v>
+        <v>0.0278</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4533</v>
+        <v>0.171</v>
       </c>
       <c r="V14" t="n">
         <v>1.0091</v>
       </c>
       <c r="W14" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.08359999999999999</v>
+        <v>-0.0804</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5726</v>
+        <v>2.3173</v>
       </c>
       <c r="E15" t="n">
-        <v>3.5649</v>
+        <v>3.1812</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9923</v>
+        <v>-0.8638</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9336</v>
+        <v>0.9514</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.5138</v>
+        <v>-0.5059</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4475</v>
+        <v>1.4573</v>
       </c>
       <c r="J15" t="n">
-        <v>2.0834</v>
+        <v>2.069</v>
       </c>
       <c r="K15" t="n">
-        <v>1.1878</v>
+        <v>1.1754</v>
       </c>
       <c r="L15" t="n">
-        <v>0.8956</v>
+        <v>0.8937</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.1497</v>
+        <v>-1.1177</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.7016</v>
+        <v>-1.6813</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5518999999999999</v>
+        <v>0.5636</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2002</v>
+        <v>-0.0602</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1089</v>
+        <v>-0.2442</v>
       </c>
       <c r="U15" t="n">
-        <v>0.09130000000000001</v>
+        <v>0.184</v>
       </c>
       <c r="V15" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="W15" t="n">
-        <v>2.5068</v>
+        <v>2.4945</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2512</v>
+        <v>1.2951</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0931</v>
+        <v>-0.2392</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3444</v>
+        <v>1.5343</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.6479</v>
+        <v>-0.6389</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.853</v>
+        <v>-0.8367</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2052</v>
+        <v>0.1978</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.3908</v>
+        <v>-0.4107</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.4573</v>
+        <v>-0.4621</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0665</v>
+        <v>0.0515</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.257</v>
+        <v>-0.2282</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3957</v>
+        <v>-0.3745</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1387</v>
+        <v>0.1463</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2601</v>
+        <v>0.2998</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1785</v>
+        <v>0.0624</v>
       </c>
       <c r="U16" t="n">
-        <v>0.08160000000000001</v>
+        <v>0.2374</v>
       </c>
       <c r="V16" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="17">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6983</v>
+        <v>-1.119</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.1188</v>
+        <v>-1.2484</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4205</v>
+        <v>0.1294</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5641</v>
+        <v>-0.5478</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2816</v>
+        <v>-0.2679</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2825</v>
+        <v>-0.2799</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1839</v>
+        <v>0.1834</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1493</v>
+        <v>0.1489</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.748</v>
+        <v>-0.7312</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3162</v>
+        <v>-0.3023</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4318</v>
+        <v>-0.4289</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8529</v>
+        <v>0.4228</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5081</v>
+        <v>0.3924</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3448</v>
+        <v>0.0305</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.5334</v>
+        <v>-0.5387999999999999</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.4498</v>
+        <v>-0.4584</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.08359999999999999</v>
+        <v>-0.0804</v>
       </c>
     </row>
     <row r="18">
@@ -1813,19 +1813,19 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.3719</v>
+        <v>-1.3424</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.2037</v>
+        <v>-1.2079</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1682</v>
+        <v>-0.1345</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1891</v>
+        <v>-0.1868</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1891</v>
+        <v>-0.1868</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1840,31 +1840,31 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1891</v>
+        <v>-0.1868</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1891</v>
+        <v>-0.1868</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0487</v>
+        <v>-0.0174</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0696</v>
+        <v>-0.0697</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0209</v>
+        <v>0.0523</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6942</v>
+        <v>-1.4582</v>
       </c>
       <c r="E19" t="n">
-        <v>0.615</v>
+        <v>0.7897999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.3092</v>
+        <v>-2.248</v>
       </c>
       <c r="G19" t="n">
-        <v>3.797</v>
+        <v>3.785</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.1529</v>
+        <v>-1.1572</v>
       </c>
       <c r="I19" t="n">
-        <v>4.9498</v>
+        <v>4.9422</v>
       </c>
       <c r="J19" t="n">
-        <v>5.544</v>
+        <v>5.5055</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3597</v>
+        <v>0.3373</v>
       </c>
       <c r="L19" t="n">
-        <v>5.1843</v>
+        <v>5.1683</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.747</v>
+        <v>-1.7205</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.5125</v>
+        <v>-1.4945</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2345</v>
+        <v>-0.226</v>
       </c>
       <c r="P19" t="n">
-        <v>-4.083</v>
+        <v>-4.0974</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4.7635</v>
+        <v>-4.7803</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7141</v>
+        <v>-0.4493</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4869</v>
+        <v>-0.251</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2271</v>
+        <v>-0.1983</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6941000000000001</v>
+        <v>-0.6966</v>
       </c>
       <c r="W19" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0155</v>
+        <v>-1.0121</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. SASTRE</t>
+          <t>A. DOORNEKAMP</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7248</v>
+        <v>-2.5621</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9777</v>
+        <v>-0.3603</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.747</v>
+        <v>-2.2018</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9899</v>
+        <v>-0.8179999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5181</v>
+        <v>-0.8283</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4718</v>
+        <v>0.0103</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.769</v>
+        <v>-0.0162</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0173</v>
+        <v>0.3792</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.7864</v>
+        <v>-0.3954</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2209</v>
+        <v>-0.8018</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5354</v>
+        <v>-1.2075</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3145</v>
+        <v>0.4057</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.1382</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.1382</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4815</v>
+        <v>-0.3878</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2087</v>
+        <v>-0.3441</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2728</v>
+        <v>-0.0436</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2534</v>
+        <v>-2.4945</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2534</v>
+        <v>-2.4945</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. DOORNEKAMP</t>
+          <t>J. SASTRE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.2854</v>
+        <v>-2.6557</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8169</v>
+        <v>-0.9815</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.4685</v>
+        <v>-1.6742</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.8355</v>
+        <v>-0.9881</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8488</v>
+        <v>-0.5143</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0133</v>
+        <v>-0.4738</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.0003</v>
+        <v>-0.7724</v>
       </c>
       <c r="K21" t="n">
-        <v>0.381</v>
+        <v>0.0172</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.3813</v>
+        <v>-0.7896</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8352000000000001</v>
+        <v>-0.2157</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.2298</v>
+        <v>-0.5315</v>
       </c>
       <c r="O21" t="n">
-        <v>0.3946</v>
+        <v>0.3159</v>
       </c>
       <c r="P21" t="n">
-        <v>1.1342</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1342</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0773</v>
+        <v>-0.4204</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8166</v>
+        <v>-0.2091</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2607</v>
+        <v>-0.2113</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.5068</v>
+        <v>-1.2472</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.5068</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.0743</v>
+        <v>-3.7493</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1443</v>
+        <v>-1.8125</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.9301</v>
+        <v>-1.9368</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.7616</v>
+        <v>-1.7584</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4315</v>
+        <v>-0.4281</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.3301</v>
+        <v>-1.3302</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.4354</v>
+        <v>-0.4535</v>
       </c>
       <c r="K22" t="n">
-        <v>0.876</v>
+        <v>0.8651</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.3115</v>
+        <v>-1.3186</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.3261</v>
+        <v>-1.3048</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.3075</v>
+        <v>-1.2932</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0186</v>
+        <v>-0.0116</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6167</v>
+        <v>-0.296</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3478</v>
+        <v>0.0068</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2689</v>
+        <v>-0.3028</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0155</v>
+        <v>-1.0121</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0155</v>
+        <v>-1.0121</v>
       </c>
     </row>
     <row r="23">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.1847</v>
+        <v>-5.6999</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.7009</v>
+        <v>-6.4611</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5163</v>
+        <v>0.7611</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.375</v>
+        <v>-1.3729</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7069</v>
+        <v>0.7174</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.0818</v>
+        <v>-2.0903</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.0511</v>
+        <v>-1.0721</v>
       </c>
       <c r="K23" t="n">
-        <v>1.3853</v>
+        <v>1.3789</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.4364</v>
+        <v>-2.4511</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.3239</v>
+        <v>-0.3007</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.6785</v>
+        <v>-0.6615</v>
       </c>
       <c r="O23" t="n">
-        <v>0.3546</v>
+        <v>0.3608</v>
       </c>
       <c r="P23" t="n">
-        <v>-7.0318</v>
+        <v>-7.0566</v>
       </c>
       <c r="Q23" t="n">
-        <v>-7.9391</v>
+        <v>-7.9671</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S23" t="n">
-        <v>1.0368</v>
+        <v>0.5506</v>
       </c>
       <c r="T23" t="n">
-        <v>1.1039</v>
+        <v>0.3992</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0672</v>
+        <v>0.1513</v>
       </c>
       <c r="V23" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="W23" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.650300000000001</v>
+        <v>-5.864999999999998</v>
       </c>
       <c r="E24" t="n">
-        <v>2.711100000000001</v>
+        <v>2.410600000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-9.3611</v>
+        <v>-8.275499999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>6.205000000000002</v>
+        <v>6.277900000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>-6.069299999999999</v>
+        <v>-5.965299999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>12.2746</v>
+        <v>12.2433</v>
       </c>
       <c r="J24" t="n">
-        <v>15.694</v>
+        <v>15.5224</v>
       </c>
       <c r="K24" t="n">
-        <v>4.0197</v>
+        <v>3.9528</v>
       </c>
       <c r="L24" t="n">
-        <v>11.6741</v>
+        <v>11.5697</v>
       </c>
       <c r="M24" t="n">
-        <v>-9.4887</v>
+        <v>-9.244400000000001</v>
       </c>
       <c r="N24" t="n">
-        <v>-10.089</v>
+        <v>-9.917900000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>0.6003999999999998</v>
+        <v>0.6737</v>
       </c>
       <c r="P24" t="n">
-        <v>-15.8783</v>
+        <v>-15.9343</v>
       </c>
       <c r="Q24" t="n">
-        <v>-23.8175</v>
+        <v>-23.9015</v>
       </c>
       <c r="R24" t="n">
-        <v>7.939100000000001</v>
+        <v>7.967099999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8014999999999999</v>
+        <v>-0.02190000000000003</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.06039999999999979</v>
+        <v>-0.04870000000000002</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7412</v>
+        <v>0.02689999999999992</v>
       </c>
       <c r="V24" t="n">
-        <v>3.8244</v>
+        <v>3.813000000000001</v>
       </c>
       <c r="W24" t="n">
-        <v>10.8949</v>
+        <v>10.8381</v>
       </c>
       <c r="X24" t="n">
-        <v>-7.070500000000001</v>
+        <v>-7.0251</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104621_W19.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104621_W19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.4733</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104621_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104621_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104621_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104621_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104621_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104621_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.6311</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104621_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104621_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-3.9709</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104621_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104621_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-11.9277</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>-1.3276</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104621_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-0.0804</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104621_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104621_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104621_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.0804</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104621_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104621_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.0121</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104621_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-2.4945</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104621_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104621_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.0121</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104621_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104621_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-7.0251</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
